--- a/artfynd/A 1615-2023 artfynd.xlsx
+++ b/artfynd/A 1615-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1615-2023 artfynd.xlsx
+++ b/artfynd/A 1615-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121142886</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1615-2023 artfynd.xlsx
+++ b/artfynd/A 1615-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121142886</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1615-2023 artfynd.xlsx
+++ b/artfynd/A 1615-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112773669</v>
+        <v>12643</v>
       </c>
       <c r="B2" t="n">
-        <v>56891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100084</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckatorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488514</v>
+        <v>488404</v>
       </c>
       <c r="R2" t="n">
-        <v>6540449</v>
+        <v>6540524</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +759,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2007-10-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Slyrik kraftledning av triviala lövträd. Mycket örnbräken. Boplats: En. Hasselmusinventering, länsstyrelsen i Örebro län, publ.nr. 2009:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,27 +784,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Hasselmusinventering i Örebro län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121142886</v>
+        <v>112773669</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -829,17 +839,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Bäckatorp, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488469</v>
+        <v>488514</v>
       </c>
       <c r="R3" t="n">
-        <v>6540429</v>
+        <v>6540450</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +898,115 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Per Karlsson Linderum, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121142886</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488469</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6540429</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Per Karlsson Linderum</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1615-2023 artfynd.xlsx
+++ b/artfynd/A 1615-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Hasselmusinventering i Örebro län</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12643</t>
         </is>
       </c>
     </row>
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112773669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>